--- a/MATERIAL_IN_OUT/Template/huongdanIssueInOut.xlsx
+++ b/MATERIAL_IN_OUT/Template/huongdanIssueInOut.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D746DE11-34AD-4837-8BAF-16CD01CAE393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80FE01E-8789-43F4-A733-98D45F86A4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7595A650-7345-43C4-BEA2-9DD7FDDC8FC4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -123,9 +123,6 @@
     <t>3. Kế toán phê duyệt</t>
   </si>
   <si>
-    <t>4. Trường hợp Out stock</t>
-  </si>
-  <si>
     <t>5. Trường hợp check giá ACCC</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
       </rPr>
       <t>1.Other Issue Materials  =&gt; và comment.</t>
     </r>
+  </si>
+  <si>
+    <t>4. Trường hợp Out stock chỉ áp dụng cho bộ phận PMS</t>
   </si>
 </sst>
 </file>
@@ -278,8 +278,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>501671</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>163284</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -302,8 +302,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="557893" y="952500"/>
-          <a:ext cx="6679314" cy="4599213"/>
+          <a:off x="557893" y="1491983"/>
+          <a:ext cx="6600072" cy="4424723"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -316,13 +316,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>13608</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>163286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>319647</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>154105</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -360,13 +360,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>122465</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>163286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>428504</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>135053</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -404,13 +404,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>367393</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>482905</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>69732</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -446,59 +446,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>353785</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>163285</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>68034</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF49DB9C-2762-6204-8D01-C7CAD4AFB79E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="966106" y="25309285"/>
-          <a:ext cx="12790715" cy="4667249"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>204107</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>189</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>352452</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>206</xdr:row>
       <xdr:rowOff>4519</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -515,7 +471,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -536,13 +492,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>231321</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>216</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>353786</xdr:colOff>
-      <xdr:row>179</xdr:row>
+      <xdr:row>233</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -559,7 +515,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -580,13 +536,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>187</xdr:row>
+      <xdr:row>241</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>156813</xdr:colOff>
-      <xdr:row>207</xdr:row>
+      <xdr:row>261</xdr:row>
       <xdr:rowOff>54960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -603,7 +559,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -624,13 +580,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>149679</xdr:colOff>
-      <xdr:row>188</xdr:row>
+      <xdr:row>242</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>217560</xdr:colOff>
-      <xdr:row>203</xdr:row>
+      <xdr:row>257</xdr:row>
       <xdr:rowOff>13993</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -647,7 +603,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -668,13 +624,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>299358</xdr:colOff>
-      <xdr:row>210</xdr:row>
+      <xdr:row>264</xdr:row>
       <xdr:rowOff>149680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>198999</xdr:colOff>
-      <xdr:row>236</xdr:row>
+      <xdr:row>290</xdr:row>
       <xdr:rowOff>188477</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -691,7 +647,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -708,61 +664,17 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>408215</xdr:colOff>
-      <xdr:row>243</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>340179</xdr:colOff>
-      <xdr:row>278</xdr:row>
-      <xdr:rowOff>7727</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE5854F-1CDF-493B-25A3-EC3B8BAD82FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1020536" y="45964928"/>
-          <a:ext cx="12178393" cy="6620799"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>122465</xdr:colOff>
-      <xdr:row>266</xdr:row>
+      <xdr:row>320</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>544286</xdr:colOff>
-      <xdr:row>269</xdr:row>
+      <xdr:row>323</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -822,13 +734,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>340179</xdr:colOff>
-      <xdr:row>279</xdr:row>
+      <xdr:row>333</xdr:row>
       <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>481212</xdr:colOff>
-      <xdr:row>312</xdr:row>
+      <xdr:row>366</xdr:row>
       <xdr:rowOff>184581</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -845,7 +757,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -866,13 +778,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>163288</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>216</xdr:row>
       <xdr:rowOff>149680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>598716</xdr:colOff>
-      <xdr:row>183</xdr:row>
+      <xdr:row>237</xdr:row>
       <xdr:rowOff>27216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -889,7 +801,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -910,13 +822,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>313764</xdr:colOff>
-      <xdr:row>393</xdr:row>
+      <xdr:row>447</xdr:row>
       <xdr:rowOff>173451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>493059</xdr:colOff>
-      <xdr:row>407</xdr:row>
+      <xdr:row>461</xdr:row>
       <xdr:rowOff>71763</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -932,8 +844,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="313764" y="75784633"/>
-          <a:ext cx="6846795" cy="2617266"/>
+          <a:off x="313764" y="85988098"/>
+          <a:ext cx="6835589" cy="2610136"/>
           <a:chOff x="1020535" y="75478821"/>
           <a:chExt cx="6649378" cy="2619741"/>
         </a:xfrm>
@@ -952,7 +864,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1025,13 +937,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>134470</xdr:colOff>
-      <xdr:row>393</xdr:row>
+      <xdr:row>447</xdr:row>
       <xdr:rowOff>94690</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>425822</xdr:colOff>
-      <xdr:row>421</xdr:row>
+      <xdr:row>475</xdr:row>
       <xdr:rowOff>120463</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1047,8 +959,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8014243" y="75705872"/>
-          <a:ext cx="13626352" cy="5411727"/>
+          <a:off x="8000999" y="85909337"/>
+          <a:ext cx="13603941" cy="5404597"/>
           <a:chOff x="7594787" y="75454249"/>
           <a:chExt cx="13954124" cy="5404597"/>
         </a:xfrm>
@@ -1067,7 +979,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1293,13 +1205,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>515471</xdr:colOff>
-      <xdr:row>410</xdr:row>
+      <xdr:row>464</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>246530</xdr:colOff>
-      <xdr:row>421</xdr:row>
+      <xdr:row>475</xdr:row>
       <xdr:rowOff>-1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1316,7 +1228,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1337,13 +1249,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>425822</xdr:colOff>
-      <xdr:row>426</xdr:row>
+      <xdr:row>480</xdr:row>
       <xdr:rowOff>5043</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>326251</xdr:colOff>
-      <xdr:row>433</xdr:row>
+      <xdr:row>487</xdr:row>
       <xdr:rowOff>43329</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1359,8 +1271,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7699458" y="81954679"/>
-          <a:ext cx="12629293" cy="1371786"/>
+          <a:off x="7687234" y="92151014"/>
+          <a:ext cx="12607899" cy="1371786"/>
           <a:chOff x="6521824" y="81976073"/>
           <a:chExt cx="13739692" cy="1371786"/>
         </a:xfrm>
@@ -1379,7 +1291,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1452,13 +1364,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>33617</xdr:colOff>
-      <xdr:row>423</xdr:row>
+      <xdr:row>477</xdr:row>
       <xdr:rowOff>33618</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>44823</xdr:colOff>
-      <xdr:row>424</xdr:row>
+      <xdr:row>478</xdr:row>
       <xdr:rowOff>168088</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1512,13 +1424,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>582707</xdr:colOff>
-      <xdr:row>423</xdr:row>
+      <xdr:row>477</xdr:row>
       <xdr:rowOff>89647</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>526678</xdr:colOff>
-      <xdr:row>433</xdr:row>
+      <xdr:row>487</xdr:row>
       <xdr:rowOff>49158</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1535,7 +1447,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1556,13 +1468,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>437</xdr:row>
+      <xdr:row>491</xdr:row>
       <xdr:rowOff>156882</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>359671</xdr:colOff>
-      <xdr:row>466</xdr:row>
+      <xdr:row>520</xdr:row>
       <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1578,8 +1490,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="606136" y="84202018"/>
-          <a:ext cx="16725353" cy="5524500"/>
+          <a:off x="605118" y="94398353"/>
+          <a:ext cx="16697847" cy="5524500"/>
           <a:chOff x="605118" y="84111353"/>
           <a:chExt cx="16697847" cy="5524500"/>
         </a:xfrm>
@@ -1598,7 +1510,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1824,13 +1736,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>51546</xdr:colOff>
-      <xdr:row>407</xdr:row>
+      <xdr:row>461</xdr:row>
       <xdr:rowOff>107577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>62751</xdr:colOff>
-      <xdr:row>409</xdr:row>
+      <xdr:row>463</xdr:row>
       <xdr:rowOff>51547</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1884,13 +1796,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>584945</xdr:colOff>
-      <xdr:row>421</xdr:row>
+      <xdr:row>475</xdr:row>
       <xdr:rowOff>69477</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>596151</xdr:colOff>
-      <xdr:row>423</xdr:row>
+      <xdr:row>477</xdr:row>
       <xdr:rowOff>13447</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1944,13 +1856,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>47065</xdr:colOff>
-      <xdr:row>400</xdr:row>
+      <xdr:row>454</xdr:row>
       <xdr:rowOff>24653</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>372035</xdr:colOff>
-      <xdr:row>406</xdr:row>
+      <xdr:row>460</xdr:row>
       <xdr:rowOff>103094</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2004,13 +1916,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>350</xdr:row>
+      <xdr:row>404</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>489857</xdr:colOff>
-      <xdr:row>385</xdr:row>
+      <xdr:row>439</xdr:row>
       <xdr:rowOff>95251</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2026,8 +1938,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="891886" y="67449370"/>
-          <a:ext cx="15963653" cy="6681108"/>
+          <a:off x="890868" y="77659967"/>
+          <a:ext cx="15937165" cy="6681108"/>
           <a:chOff x="890868" y="67372967"/>
           <a:chExt cx="15937165" cy="6681108"/>
         </a:xfrm>
@@ -2046,7 +1958,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2119,13 +2031,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>326572</xdr:colOff>
-      <xdr:row>314</xdr:row>
+      <xdr:row>368</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>524763</xdr:colOff>
-      <xdr:row>348</xdr:row>
+      <xdr:row>402</xdr:row>
       <xdr:rowOff>117922</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2141,8 +2053,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="932708" y="60645798"/>
-          <a:ext cx="15957737" cy="6458851"/>
+          <a:off x="931690" y="70856395"/>
+          <a:ext cx="15931249" cy="6458851"/>
           <a:chOff x="931690" y="60569395"/>
           <a:chExt cx="15931249" cy="6458851"/>
         </a:xfrm>
@@ -2161,7 +2073,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2292,16 +2204,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>365312</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>40341</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12327</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>101976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>62754</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>62753</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>572621</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>23535</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2315,8 +2227,8 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16098371" y="3301253"/>
+        <a:xfrm rot="5400000">
+          <a:off x="7100047" y="5788962"/>
           <a:ext cx="302559" cy="1165412"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
@@ -2354,13 +2266,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>439431</xdr:colOff>
-      <xdr:row>210</xdr:row>
+      <xdr:row>264</xdr:row>
       <xdr:rowOff>128066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>481853</xdr:colOff>
-      <xdr:row>213</xdr:row>
+      <xdr:row>267</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2426,8 +2338,8 @@
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>394607</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>68035</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2442,8 +2354,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7807035" y="1572242"/>
-          <a:ext cx="7740981" cy="4626429"/>
+          <a:off x="7794811" y="1560018"/>
+          <a:ext cx="7727737" cy="4446335"/>
           <a:chOff x="7881256" y="1578427"/>
           <a:chExt cx="7821387" cy="4626429"/>
         </a:xfrm>
@@ -2462,7 +2374,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2533,130 +2445,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>316485</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>397726</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>76996</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="67" name="Group 66">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BDFCA05-F77B-85CA-D298-7AD419F38205}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="16682167" y="1422565"/>
-          <a:ext cx="16446923" cy="5166067"/>
-          <a:chOff x="16849164" y="1428750"/>
-          <a:chExt cx="16613919" cy="5166067"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="65" name="Picture 64">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF1E2D1-CBFE-7266-ACEC-219500B5C808}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="16849164" y="1428750"/>
-            <a:ext cx="16613919" cy="5166067"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="66" name="Rectangle 65">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E18F198-CF9F-4EB8-8EF0-80B1D43CCB4A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="21260600" y="5731330"/>
-            <a:ext cx="4103114" cy="421822"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="38100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>130627</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>62639</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>74566</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2672,8 +2469,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="891886" y="7508172"/>
-          <a:ext cx="13111889" cy="5658939"/>
+          <a:off x="890868" y="17768686"/>
+          <a:ext cx="13089477" cy="5658939"/>
           <a:chOff x="891886" y="7508172"/>
           <a:chExt cx="13111889" cy="5658939"/>
         </a:xfrm>
@@ -2692,7 +2489,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2765,13 +2562,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>326571</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>158</xdr:row>
       <xdr:rowOff>89371</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2787,8 +2584,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="285750" y="14042571"/>
-          <a:ext cx="13981957" cy="6239800"/>
+          <a:off x="285750" y="24295953"/>
+          <a:ext cx="13958527" cy="6239800"/>
           <a:chOff x="285750" y="14042571"/>
           <a:chExt cx="13981957" cy="6239800"/>
         </a:xfrm>
@@ -2807,7 +2604,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2880,13 +2677,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>503464</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>449036</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>183</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2902,8 +2699,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="503464" y="21197455"/>
-          <a:ext cx="13886708" cy="3946071"/>
+          <a:off x="503464" y="31443706"/>
+          <a:ext cx="13863278" cy="3946071"/>
           <a:chOff x="503464" y="21197455"/>
           <a:chExt cx="13886708" cy="3946071"/>
         </a:xfrm>
@@ -2922,7 +2719,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2985,6 +2782,1008 @@
           <a:p>
             <a:pPr algn="l"/>
             <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>78441</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>56031</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>33618</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>168090</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Arrow: Right 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FF7F09A-1A3D-448D-9DE1-5115E87F9E80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7771279" y="12220017"/>
+          <a:ext cx="302559" cy="1165412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>526676</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>313765</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>104638</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="32" name="Group 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058ECDF0-4D43-D26E-79AC-C5FDDB60BD22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="526676" y="13110882"/>
+          <a:ext cx="16730383" cy="3208668"/>
+          <a:chOff x="526676" y="13110882"/>
+          <a:chExt cx="16730383" cy="3208668"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="27" name="Picture 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81256DBC-0F7E-420F-2EF1-A3C36AA499FD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="526676" y="13290177"/>
+            <a:ext cx="13973734" cy="3029373"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="30" name="Rectangle 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2E1C244-B581-4CE0-9329-FC09FA79DD72}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13234144" y="13514294"/>
+            <a:ext cx="1456767" cy="840441"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="31" name="Speech Bubble: Rectangle with Corners Rounded 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F078926E-8B8A-E5B4-BC3F-C608ECA933D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="15396882" y="13110882"/>
+            <a:ext cx="1860177" cy="874059"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val -103449"/>
+              <a:gd name="adj2" fmla="val 31730"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Nhập</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> lại số request NO nếu trường hợp muốn update lại thông tin reqesst vừa upload</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>353785</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>68034</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="71" name="Group 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB678C7D-13BA-132A-A47B-B86EE8CAD023}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="958903" y="36459138"/>
+          <a:ext cx="12639435" cy="4667249"/>
+          <a:chOff x="958903" y="36459138"/>
+          <a:chExt cx="12639435" cy="4667249"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="10" name="Picture 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF49DB9C-2762-6204-8D01-C7CAD4AFB79E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="958903" y="36459138"/>
+            <a:ext cx="12639435" cy="4667249"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="64" name="Rectangle 63">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1384B2D0-6B10-8BE1-FDD8-D031FA050762}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5546912" y="40262735"/>
+            <a:ext cx="1086970" cy="369794"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="69" name="Speech Bubble: Rectangle with Corners Rounded 68">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE6110E9-15AB-EEEB-FB19-69166EBDC42C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7799294" y="39691235"/>
+            <a:ext cx="1243853" cy="885265"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val -139752"/>
+              <a:gd name="adj2" fmla="val 25791"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Kế toán</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> check lại giá tại thời điểm cập nhật lại giá từ SAP</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>408215</xdr:colOff>
+      <xdr:row>297</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>340179</xdr:colOff>
+      <xdr:row>332</xdr:row>
+      <xdr:rowOff>7727</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="78" name="Group 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C710116F-5515-272F-EBD0-87BD3A091D5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1013333" y="57249252"/>
+          <a:ext cx="12034317" cy="6620799"/>
+          <a:chOff x="1013333" y="57249252"/>
+          <a:chExt cx="12034317" cy="6620799"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="18" name="Picture 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE5854F-1CDF-493B-25A3-EC3B8BAD82FB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1013333" y="57249252"/>
+            <a:ext cx="12034317" cy="6620799"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="77" name="Rectangle 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FBCA81-1006-7E33-A975-1B3E02B2EC61}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10679206" y="57643059"/>
+            <a:ext cx="1613647" cy="1456765"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>224117</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>85164</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="83" name="Group 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54DFB92D-9C5C-DB00-CB2E-18AFE1FCD62F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="705970" y="6689911"/>
+          <a:ext cx="13435853" cy="6371665"/>
+          <a:chOff x="683558" y="6790764"/>
+          <a:chExt cx="13435853" cy="6371665"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="28" name="Group 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B2CBEC7-0D98-F67D-C7C3-97F2FBFCE052}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="683558" y="6790764"/>
+            <a:ext cx="13435853" cy="5715001"/>
+            <a:chOff x="683558" y="6790764"/>
+            <a:chExt cx="13435853" cy="5715001"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="17" name="Picture 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1C369DE-316F-A6F1-642B-7E3FFF43F479}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="683558" y="6790764"/>
+              <a:ext cx="13435853" cy="5715001"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="Rectangle 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76ABBBFF-EA9F-4C1F-A181-3EDFAE7636FE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6813177" y="11766177"/>
+              <a:ext cx="952500" cy="467591"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="Rectangle 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDC0780F-CC59-4E60-A577-93F5EEF71662}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5804646" y="11766175"/>
+            <a:ext cx="952500" cy="467591"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="79" name="Speech Bubble: Rectangle with Corners Rounded 78">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57E051AC-FC1A-1698-E0F0-3C5C61808E5C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8538882" y="12304059"/>
+            <a:ext cx="1524000" cy="750794"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val -106127"/>
+              <a:gd name="adj2" fmla="val -65858"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Download</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> template form A &amp; form B</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="80" name="Speech Bubble: Rectangle with Corners Rounded 79">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{591C18B3-B394-4ADC-B14B-10744DBAA6B8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5217459" y="12411635"/>
+            <a:ext cx="1524000" cy="750794"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 37255"/>
+              <a:gd name="adj2" fmla="val -67350"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Sau khi nhập</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> xong dữ liệu thì sẽ thực hiện upload issue out</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="81" name="Rectangle 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD334BBC-F86F-4A30-B445-1DED6664EDE8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4157381" y="12180794"/>
+            <a:ext cx="952500" cy="324972"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="82" name="Speech Bubble: Rectangle with Corners Rounded 81">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1284E8AC-FFA1-4BE6-B64E-776A25BDC037}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1963271" y="11611535"/>
+            <a:ext cx="1524000" cy="750794"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 92402"/>
+              <a:gd name="adj2" fmla="val 44590"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Export</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> scrap list cho hệ thống Scraps.</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -3311,7 +4110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D642923-020E-4F3D-A307-B18722D4CE25}">
-  <dimension ref="A3:Y437"/>
+  <dimension ref="A3:Y491"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
@@ -3324,70 +4123,70 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+    <row r="88" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B36" s="3" t="s">
+    <row r="90" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B90" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B70" s="3" t="s">
+    <row r="124" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B124" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B108" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B134" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="162" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B162" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B188" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B216" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="25:25" x14ac:dyDescent="0.25">
-      <c r="Y184" s="2"/>
+    <row r="238" spans="25:25" x14ac:dyDescent="0.25">
+      <c r="Y238" s="2"/>
     </row>
-    <row r="209" spans="3:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C209" s="3" t="s">
+    <row r="263" spans="3:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C263" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
+    <row r="295" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A295" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A443" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A389" s="3" t="s">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B445" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B391" s="5" t="s">
+    <row r="451" spans="7:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="G451" s="3"/>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B491" s="5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="397" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="G397" s="3"/>
-    </row>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B437" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/MATERIAL_IN_OUT/Template/huongdanIssueInOut.xlsx
+++ b/MATERIAL_IN_OUT/Template/huongdanIssueInOut.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80FE01E-8789-43F4-A733-98D45F86A4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF00CB8B-A378-47FF-A6DA-DABCACD7C0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7595A650-7345-43C4-BEA2-9DD7FDDC8FC4}"/>
   </bookViews>
@@ -2850,193 +2850,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>526676</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>134470</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>313765</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>104638</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="32" name="Group 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058ECDF0-4D43-D26E-79AC-C5FDDB60BD22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="526676" y="13110882"/>
-          <a:ext cx="16730383" cy="3208668"/>
-          <a:chOff x="526676" y="13110882"/>
-          <a:chExt cx="16730383" cy="3208668"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="27" name="Picture 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81256DBC-0F7E-420F-2EF1-A3C36AA499FD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="526676" y="13290177"/>
-            <a:ext cx="13973734" cy="3029373"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="Rectangle 29">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2E1C244-B581-4CE0-9329-FC09FA79DD72}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13234144" y="13514294"/>
-            <a:ext cx="1456767" cy="840441"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="28575">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="Speech Bubble: Rectangle with Corners Rounded 30">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F078926E-8B8A-E5B4-BC3F-C608ECA933D6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="15396882" y="13110882"/>
-            <a:ext cx="1860177" cy="874059"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRoundRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -103449"/>
-              <a:gd name="adj2" fmla="val 31730"/>
-              <a:gd name="adj3" fmla="val 16667"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Nhập</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t> lại số request NO nếu trường hợp muốn update lại thông tin reqesst vừa upload</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>353785</xdr:colOff>
       <xdr:row>188</xdr:row>
@@ -3081,7 +2894,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3268,7 +3081,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3402,7 +3215,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -3778,6 +3591,332 @@
                 </a:solidFill>
               </a:rPr>
               <a:t> scrap list cho hệ thống Scraps.</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>313765</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>104638</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="67" name="Group 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77BD7F5B-9FE9-23F4-8D48-705D5186825D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="358588" y="12012707"/>
+          <a:ext cx="16898471" cy="4306843"/>
+          <a:chOff x="358588" y="12012707"/>
+          <a:chExt cx="16898471" cy="4306843"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="32" name="Group 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058ECDF0-4D43-D26E-79AC-C5FDDB60BD22}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="526676" y="13110882"/>
+            <a:ext cx="16730383" cy="3208668"/>
+            <a:chOff x="526676" y="13110882"/>
+            <a:chExt cx="16730383" cy="3208668"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="27" name="Picture 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81256DBC-0F7E-420F-2EF1-A3C36AA499FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="526676" y="13290177"/>
+              <a:ext cx="13973734" cy="3029373"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="30" name="Rectangle 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2E1C244-B581-4CE0-9329-FC09FA79DD72}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13234144" y="13514294"/>
+              <a:ext cx="1456767" cy="840441"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr lang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="Speech Bubble: Rectangle with Corners Rounded 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F078926E-8B8A-E5B4-BC3F-C608ECA933D6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15396882" y="13110882"/>
+              <a:ext cx="1860177" cy="874059"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRoundRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -103449"/>
+                <a:gd name="adj2" fmla="val 31730"/>
+                <a:gd name="adj3" fmla="val 16667"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Nhập</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> lại số request NO nếu trường hợp muốn update lại thông tin reqesst vừa upload</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="65" name="Rectangle 64">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CE906B9-A6E0-75B0-5F51-DCDC25C35D54}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="448235" y="13312588"/>
+            <a:ext cx="818030" cy="1199030"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="66" name="Speech Bubble: Rectangle with Corners Rounded 65">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8875C424-BB16-945F-A784-C6E1B2ADC5C0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="358588" y="12012707"/>
+            <a:ext cx="1389530" cy="1165412"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Bắt</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> buộc phải chọn theo bộ lọc theo master và copy xuống các dòng dưới</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" sz="1100">
               <a:solidFill>
